--- a/artfynd/A 61354-2019 artfynd.xlsx
+++ b/artfynd/A 61354-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61354-2019 artfynd.xlsx
+++ b/artfynd/A 61354-2019 artfynd.xlsx
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118057888</v>
+        <v>118057889</v>
       </c>
       <c r="B4" t="n">
-        <v>97859</v>
+        <v>97754</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,26 +943,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631588</v>
+        <v>631590</v>
       </c>
       <c r="R4" t="n">
-        <v>6712887</v>
+        <v>6712889</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca. 20 blommande plantor.</t>
+          <t>Ca. 30 blommande plantor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118057889</v>
+        <v>118057888</v>
       </c>
       <c r="B5" t="n">
-        <v>97754</v>
+        <v>97859</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,26 +1069,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631590</v>
+        <v>631588</v>
       </c>
       <c r="R5" t="n">
-        <v>6712889</v>
+        <v>6712887</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca. 30 blommande plantor.</t>
+          <t>Ca. 20 blommande plantor.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61354-2019 artfynd.xlsx
+++ b/artfynd/A 61354-2019 artfynd.xlsx
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118057861</v>
+        <v>118057889</v>
       </c>
       <c r="B3" t="n">
-        <v>97814</v>
+        <v>97756</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,26 +822,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>223591</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,16 +849,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hålldammen vid Älvkarleö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631561</v>
+        <v>631590</v>
       </c>
       <c r="R3" t="n">
-        <v>6712890</v>
+        <v>6712889</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +900,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca. 5 plantor.</t>
+          <t>Ca. 30 blommande plantor.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118057889</v>
+        <v>118057888</v>
       </c>
       <c r="B4" t="n">
-        <v>97754</v>
+        <v>97861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,26 +948,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -981,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631590</v>
+        <v>631588</v>
       </c>
       <c r="R4" t="n">
-        <v>6712889</v>
+        <v>6712887</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,7 +1026,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ca. 30 blommande plantor.</t>
+          <t>Ca. 20 blommande plantor.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118057888</v>
+        <v>118057861</v>
       </c>
       <c r="B5" t="n">
-        <v>97859</v>
+        <v>97816</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,26 +1074,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1096,21 +1101,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hålldammen vid Älvkarleö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631588</v>
+        <v>631561</v>
       </c>
       <c r="R5" t="n">
-        <v>6712887</v>
+        <v>6712890</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ca. 20 blommande plantor.</t>
+          <t>Ca. 5 plantor.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61354-2019 artfynd.xlsx
+++ b/artfynd/A 61354-2019 artfynd.xlsx
@@ -1179,10 +1179,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118231464</v>
+        <v>118231540</v>
       </c>
       <c r="B6" t="n">
-        <v>97764</v>
+        <v>97824</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,26 +1195,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>223591</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1222,21 +1222,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hålldammen vid Älvkarleö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631631</v>
+        <v>631603</v>
       </c>
       <c r="R6" t="n">
-        <v>6712933</v>
+        <v>6712899</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,7 +1268,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4 blommande plantor, intill nygrävt dike, (nygrävt - ej rensning av gammalt dike).</t>
+          <t>Ca. 10 plantor.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,7 +1282,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Nytt kalhygge från ca. 2022, i fuktigt parti som tidigare var en älvtyll, innan kraftverket Lanforsen byggdes på 1920-talet.</t>
+          <t>Litet, kvarlämnat, fuktigt blandskogsparti på ett nytt kalhygge från ca. 2022. Biotopen var tidigare en älvtyll, innan kraftverket Lanforsen byggdes på 1920-talet.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1431,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118231540</v>
+        <v>118231541</v>
       </c>
       <c r="B8" t="n">
-        <v>97824</v>
+        <v>97869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1447,26 +1442,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1474,16 +1469,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hålldammen vid Älvkarleö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631603</v>
+        <v>631599</v>
       </c>
       <c r="R8" t="n">
-        <v>6712899</v>
+        <v>6712898</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ca. 10 plantor.</t>
+          <t>Ca. 20 blommande plantor.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118231541</v>
+        <v>118231464</v>
       </c>
       <c r="B10" t="n">
-        <v>97869</v>
+        <v>97764</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,26 +1690,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>223591</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631599</v>
+        <v>631631</v>
       </c>
       <c r="R10" t="n">
-        <v>6712898</v>
+        <v>6712933</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca. 20 blommande plantor.</t>
+          <t>4 blommande plantor, intill nygrävt dike, (nygrävt - ej rensning av gammalt dike).</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Litet, kvarlämnat, fuktigt blandskogsparti på ett nytt kalhygge från ca. 2022. Biotopen var tidigare en älvtyll, innan kraftverket Lanforsen byggdes på 1920-talet.</t>
+          <t>Nytt kalhygge från ca. 2022, i fuktigt parti som tidigare var en älvtyll, innan kraftverket Lanforsen byggdes på 1920-talet.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
